--- a/data/trans_dic/IP43-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP43-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones</t>
+          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 27,17</t>
+          <t>13,1; 27,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 17,4</t>
+          <t>6,24; 17,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 30,62</t>
+          <t>16,7; 31,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 19,29</t>
+          <t>8,61; 19,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 26,77</t>
+          <t>16,87; 26,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,38</t>
+          <t>8,7; 16,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 27,09</t>
+          <t>13,05; 27,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 11,4</t>
+          <t>3,59; 11,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 26,93</t>
+          <t>14,48; 26,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,06</t>
+          <t>4,92; 12,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,29; 24,99</t>
+          <t>15,39; 25,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,92</t>
+          <t>5,07; 10,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 35,37</t>
+          <t>19,45; 34,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 20,52</t>
+          <t>7,16; 20,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 34,21</t>
+          <t>18,51; 34,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 22,77</t>
+          <t>9,86; 24,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,11; 32,19</t>
+          <t>21,3; 31,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 20,32</t>
+          <t>10,01; 19,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,2</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 26,89</t>
+          <t>16,9; 26,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 19,28</t>
+          <t>11,91; 19,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 28,3</t>
+          <t>19,19; 28,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 16,01</t>
+          <t>8,77; 16,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,87</t>
+          <t>19,51; 25,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 16,52</t>
+          <t>11,42; 16,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,45; 37,27</t>
+          <t>24,2; 36,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,48; 24,44</t>
+          <t>12,79; 23,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 33,8</t>
+          <t>21,1; 33,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,66</t>
+          <t>8,44; 18,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,17; 33,32</t>
+          <t>24,96; 33,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 19,39</t>
+          <t>12,1; 18,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 20,98</t>
+          <t>6,02; 21,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,96</t>
+          <t>0,98; 8,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 15,15</t>
+          <t>4,51; 15,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 13,85</t>
+          <t>3,2; 15,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 15,07</t>
+          <t>6,52; 14,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 9,67</t>
+          <t>2,85; 10,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,01</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,22; 25,3</t>
+          <t>20,08; 25,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,86</t>
+          <t>10,74; 14,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,24; 25,35</t>
+          <t>19,89; 25,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 14,14</t>
+          <t>10,0; 13,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,92; 24,41</t>
+          <t>20,75; 24,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,96; 13,9</t>
+          <t>11,01; 13,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones (tasa de respuesta: 99,69%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>17399</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9100</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20183</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37582</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22503</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11678; 24363</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5184; 14324</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14627; 27470</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8593; 19656</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29826; 47441</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>15908; 30181</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>17905</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7311</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9335</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37271</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16646</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12057; 25073</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3799; 12110</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14010; 26086</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5549; 14536</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29125; 47775</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11081; 24001</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23007</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7810</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12005</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45180</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>19815</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16755; 30076</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4429; 12657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15839; 29467</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7439; 18377</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36585; 54727</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13742; 26900</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>43702</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34471</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52782</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25544</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96484</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>60015</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>34599; 54671</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26638; 44019</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>43278; 63536</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18494; 34380</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>83936; 111786</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>49610; 71027</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>44272</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24785</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38595</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18205</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82867</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>42990</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>35729; 53454</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17423; 32107</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29757; 46833</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12078; 26161</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>72062; 97023</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33788; 52792</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>6622</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5083</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13071</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>7129</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3247; 11625</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>598; 5487</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11303</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2168; 10205</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8264; 18811</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3670; 13343</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>152907</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>85523</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>159548</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>83574</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>312455</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>169098</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>135336; 170323</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>72094; 100437</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>141107; 177467</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>70948; 98808</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>286989; 338465</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>152098; 190126</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>